--- a/products.xlsx
+++ b/products.xlsx
@@ -1,64 +1,156 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\gamev2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Productos" sheetId="1" r:id="rId1"/>
+    <sheet name="Instrucciones" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+  <si>
+    <t>Titulo</t>
+  </si>
+  <si>
+    <t>Descripcion</t>
+  </si>
+  <si>
+    <t>Precio</t>
+  </si>
+  <si>
+    <t>Foto</t>
+  </si>
+  <si>
+    <t>Placa de video RTX 4060</t>
+  </si>
+  <si>
+    <t>8GB GDDR6, ideal para gaming en 1080p/1440p con RTX activado.</t>
+  </si>
+  <si>
+    <t>Memoria RAM 16GB DDR4</t>
+  </si>
+  <si>
+    <t>Kit 2x8GB 3200MHz, compatible con la mayoria de placas madre gamer.</t>
+  </si>
+  <si>
+    <t>Teclado mecanico RGB</t>
+  </si>
+  <si>
+    <t>Switches rojos, retroiluminado, ideal para gaming y competencia.</t>
+  </si>
+  <si>
+    <t>Como completar esta planilla</t>
+  </si>
+  <si>
+    <t>Titulo: nombre corto del producto (ej: 'Placa de video RTX 4060').</t>
+  </si>
+  <si>
+    <t>Descripcion: 1-2 lineas contando lo principal del producto.</t>
+  </si>
+  <si>
+    <t>Precio: solo el numero, sin simbolo $ ni puntos (ej: 550000). La pagina lo formatea sola.</t>
+  </si>
+  <si>
+    <t>Foto: pego aca el link directo a la imagen del producto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   -&gt; Subi las fotos a la carpeta /productos dentro de tu proyecto de Vercel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      y pega la URL final, por ejemplo:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      https://tu-sitio.vercel.app/productos/nombre-foto.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   -&gt; O si ya tenes la foto subida a internet (Instagram, Drive publico, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      pega ese link directo a la imagen.</t>
+  </si>
+  <si>
+    <t>Las filas amarillas de la hoja 'Productos' son un ejemplo: borralas o</t>
+  </si>
+  <si>
+    <t>sobreescribilas con tus productos reales. No cambies los nombres de las columnas.</t>
+  </si>
+  <si>
+    <t>Cuando termines, subi este archivo como 'products.xlsx' a la raiz de tu</t>
+  </si>
+  <si>
+    <t>proyecto (al lado de index.html) y volve a publicar en Vercel. El catalogo</t>
+  </si>
+  <si>
+    <t>de la pagina se actualiza solo, leyendo esta planilla.</t>
+  </si>
+  <si>
+    <t>https://www.gamingcity.com.ar/thumb/000000000001424954958imagen-14249_800x800.jpg</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTsCC4MrWGearck2JCnDYV_rfejzX_gEJsu0LkzeFFQ1Q&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRb8SToVElm5N7DSp1cmjiL89SMr02i2l80N9qXPfFZ5Q&amp;s=10</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="Arial"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="13"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F1B2E"/>
-        <bgColor rgb="001F1B2E"/>
+        <fgColor rgb="FF1F1B2E"/>
+        <bgColor rgb="FF1F1B2E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF6CC"/>
-        <bgColor rgb="00FFF6CC"/>
+        <fgColor rgb="FFFFF6CC"/>
+        <bgColor rgb="FFFFF6CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,87 +167,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -443,100 +476,70 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Titulo</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Precio</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Foto</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Placa de video RTX 4060</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>8GB GDDR6, ideal para gaming en 1080p/1440p con RTX activado.</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
+    <row r="1" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3">
         <v>550000</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>https://tusitio.vercel.app/productos/rtx4060.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Memoria RAM 16GB DDR4</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Kit 2x8GB 3200MHz, compatible con la mayoria de placas madre gamer.</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="D2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3">
         <v>65000</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>https://tusitio.vercel.app/productos/ram16gb.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Teclado mecanico RGB</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Switches rojos, retroiluminado, ideal para gaming y competencia.</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="D3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3">
         <v>78000</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>https://tusitio.vercel.app/productos/teclado.jpg</t>
-        </is>
+      <c r="D4" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -545,129 +548,95 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Como completar esta planilla</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Titulo: nombre corto del producto (ej: 'Placa de video RTX 4060').</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Descripcion: 1-2 lineas contando lo principal del producto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Precio: solo el numero, sin simbolo $ ni puntos (ej: 550000). La pagina lo formatea sola.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Foto: pego aca el link directo a la imagen del producto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   -&gt; Subi las fotos a la carpeta /productos dentro de tu proyecto de Vercel</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      y pega la URL final, por ejemplo:</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      https://tu-sitio.vercel.app/productos/nombre-foto.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   -&gt; O si ya tenes la foto subida a internet (Instagram, Drive publico, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      pega ese link directo a la imagen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Las filas amarillas de la hoja 'Productos' son un ejemplo: borralas o</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>sobreescribilas con tus productos reales. No cambies los nombres de las columnas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Cuando termines, subi este archivo como 'products.xlsx' a la raiz de tu</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>proyecto (al lado de index.html) y volve a publicar en Vercel. El catalogo</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>de la pagina se actualiza solo, leyendo esta planilla.</t>
-        </is>
+    <row r="1" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -1,156 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\gamev2\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Productos" sheetId="1" r:id="rId1"/>
-    <sheet name="Instrucciones" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
-  <si>
-    <t>Titulo</t>
-  </si>
-  <si>
-    <t>Descripcion</t>
-  </si>
-  <si>
-    <t>Precio</t>
-  </si>
-  <si>
-    <t>Foto</t>
-  </si>
-  <si>
-    <t>Placa de video RTX 4060</t>
-  </si>
-  <si>
-    <t>8GB GDDR6, ideal para gaming en 1080p/1440p con RTX activado.</t>
-  </si>
-  <si>
-    <t>Memoria RAM 16GB DDR4</t>
-  </si>
-  <si>
-    <t>Kit 2x8GB 3200MHz, compatible con la mayoria de placas madre gamer.</t>
-  </si>
-  <si>
-    <t>Teclado mecanico RGB</t>
-  </si>
-  <si>
-    <t>Switches rojos, retroiluminado, ideal para gaming y competencia.</t>
-  </si>
-  <si>
-    <t>Como completar esta planilla</t>
-  </si>
-  <si>
-    <t>Titulo: nombre corto del producto (ej: 'Placa de video RTX 4060').</t>
-  </si>
-  <si>
-    <t>Descripcion: 1-2 lineas contando lo principal del producto.</t>
-  </si>
-  <si>
-    <t>Precio: solo el numero, sin simbolo $ ni puntos (ej: 550000). La pagina lo formatea sola.</t>
-  </si>
-  <si>
-    <t>Foto: pego aca el link directo a la imagen del producto.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   -&gt; Subi las fotos a la carpeta /productos dentro de tu proyecto de Vercel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      y pega la URL final, por ejemplo:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      https://tu-sitio.vercel.app/productos/nombre-foto.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   -&gt; O si ya tenes la foto subida a internet (Instagram, Drive publico, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      pega ese link directo a la imagen.</t>
-  </si>
-  <si>
-    <t>Las filas amarillas de la hoja 'Productos' son un ejemplo: borralas o</t>
-  </si>
-  <si>
-    <t>sobreescribilas con tus productos reales. No cambies los nombres de las columnas.</t>
-  </si>
-  <si>
-    <t>Cuando termines, subi este archivo como 'products.xlsx' a la raiz de tu</t>
-  </si>
-  <si>
-    <t>proyecto (al lado de index.html) y volve a publicar en Vercel. El catalogo</t>
-  </si>
-  <si>
-    <t>de la pagina se actualiza solo, leyendo esta planilla.</t>
-  </si>
-  <si>
-    <t>https://www.gamingcity.com.ar/thumb/000000000001424954958imagen-14249_800x800.jpg</t>
-  </si>
-  <si>
-    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTsCC4MrWGearck2JCnDYV_rfejzX_gEJsu0LkzeFFQ1Q&amp;s=10</t>
-  </si>
-  <si>
-    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRb8SToVElm5N7DSp1cmjiL89SMr02i2l80N9qXPfFZ5Q&amp;s=10</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="13"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F1B2E"/>
-        <bgColor rgb="FF1F1B2E"/>
+        <fgColor rgb="001F1B2E"/>
+        <bgColor rgb="001F1B2E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF6CC"/>
-        <bgColor rgb="FFFFF6CC"/>
+        <fgColor rgb="00FFF6CC"/>
+        <bgColor rgb="00FFF6CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -167,28 +75,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -476,70 +443,140 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="46" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="46" customWidth="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Titulo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Precio</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Placa de video RTX 4060</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>8GB GDDR6, ideal para gaming en 1080p/1440p con RTX activado.</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>550000</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>https://tusitio.vercel.app/productos/rtx4060.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Memoria RAM 16GB DDR4</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Kit 2x8GB 3200MHz, compatible con la mayoria de placas madre gamer.</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>65000</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>https://tusitio.vercel.app/productos/ram16gb.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Teclado mecanico RGB</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Switches rojos, retroiluminado, ideal para gaming y competencia.</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>78000</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>27</v>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>https://tusitio.vercel.app/productos/teclado.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Monitor 24 pulgadas 144Hz</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Full HD, panel IPS, ideal para gaming competitivo.</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://tusitio.vercel.app/productos/monitor.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Mouse gamer inalambrico</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Sensor de alta precision, bateria de larga duracion.</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://tusitio.vercel.app/productos/mouse.jpg</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -548,95 +585,167 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="90" customWidth="1"/>
+    <col width="90" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>24</v>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Como completar esta planilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Titulo: nombre corto del producto (ej: Placa de video RTX 4060).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Descripcion: 1-2 lineas contando lo principal del producto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Precio: solo el numero, sin simbolo $ ni puntos (ej: 550000). La pagina lo formatea sola.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Foto: pego aca el link directo a la imagen del producto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   -&gt; Subi las fotos a la carpeta /productos dentro de tu proyecto de Vercel</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      y pega la URL final, por ejemplo:</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      https://tu-sitio.vercel.app/productos/nombre-foto.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   -&gt; O si ya tenes la foto subida a internet (Instagram, Drive publico, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      pega ese link directo a la imagen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Maximo 10 productos: la pagina solo muestra los primeros 10 renglones con Titulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>completo. Se ven en un carrusel horizontal (se desliza con el mouse, el dedo o</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>las flechas), asi que no importa si cargas 2 o 10: nunca quedan casilleros vacios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Las filas amarillas de la hoja Productos son un ejemplo: borralas o</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>sobreescribilas con tus productos reales. No cambies los nombres de las columnas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Para agregar un producto nuevo, simplemente escribi en la siguiente fila libre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Cuando termines, subi este archivo como products.xlsx a la raiz de tu</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>proyecto (al lado de index.html) como ARCHIVO subido (Add file -&gt; Upload files</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>en GitHub), no pegando el contenido a mano. El catalogo de la pagina se</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>actualiza solo, leyendo esta planilla.</t>
+        </is>
       </c>
     </row>
   </sheetData>
